--- a/data/trans_bre/LAWTONB_2R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R2-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 22,01</t>
+          <t>-19,73; 22,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 48,79</t>
+          <t>12,76; 51,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,37; 48,7</t>
+          <t>7,01; 46,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 16,57</t>
+          <t>-10,13; 19,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,62; 160,25</t>
+          <t>-59,53; 159,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,97; 244,85</t>
+          <t>34,08; 278,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,56; 343,4</t>
+          <t>20,31; 346,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 41,34</t>
+          <t>-17,94; 50,21</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 12,35</t>
+          <t>-16,78; 11,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 29,43</t>
+          <t>-3,15; 27,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 30,66</t>
+          <t>6,52; 29,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,17; 33,6</t>
+          <t>12,32; 34,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,22; 78,6</t>
+          <t>-49,02; 70,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 148,1</t>
+          <t>-9,06; 135,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,41; 293,19</t>
+          <t>30,16; 291,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,93; 240,41</t>
+          <t>44,79; 254,72</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 36,97</t>
+          <t>6,13; 37,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 22,78</t>
+          <t>-8,36; 23,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 13,43</t>
+          <t>-14,21; 12,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 27,64</t>
+          <t>4,0; 26,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,75; 317,77</t>
+          <t>13,76; 311,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 142,79</t>
+          <t>-25,79; 133,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,31; 89,76</t>
+          <t>-51,89; 78,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 93,67</t>
+          <t>9,7; 95,05</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 31,7</t>
+          <t>0,57; 31,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 28,31</t>
+          <t>-4,56; 28,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 23,94</t>
+          <t>-4,77; 23,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 20,32</t>
+          <t>1,99; 21,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 173,5</t>
+          <t>1,51; 172,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 125,66</t>
+          <t>-10,04; 118,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 150,81</t>
+          <t>-18,27; 145,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 116,06</t>
+          <t>5,44; 126,2</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 28,34</t>
+          <t>-13,89; 29,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 42,66</t>
+          <t>-3,82; 42,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,4; 54,12</t>
+          <t>18,79; 52,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 15,1</t>
+          <t>-10,38; 15,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 163,1</t>
+          <t>-35,66; 187,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 288,97</t>
+          <t>-12,68; 289,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,65; 963,2</t>
+          <t>77,59; 937,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 88,94</t>
+          <t>-30,06; 92,56</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 18,23</t>
+          <t>-16,33; 18,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 11,81</t>
+          <t>-23,15; 11,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 20,24</t>
+          <t>-13,55; 20,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 22,84</t>
+          <t>-0,65; 22,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,12; 68,46</t>
+          <t>-34,39; 65,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,58; 47,37</t>
+          <t>-54,33; 44,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,05; 88,89</t>
+          <t>-37,15; 89,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 70,83</t>
+          <t>-1,49; 66,5</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,8; 28,16</t>
+          <t>3,37; 25,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 20,52</t>
+          <t>-2,49; 21,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 29,46</t>
+          <t>4,4; 29,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 23,54</t>
+          <t>-20,72; 23,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,25; 213,29</t>
+          <t>10,09; 189,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 104,47</t>
+          <t>-7,53; 112,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,68; 158,9</t>
+          <t>12,21; 156,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-78,86; 139,5</t>
+          <t>-84,79; 136,14</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 10,43</t>
+          <t>-10,48; 12,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,94; 22,72</t>
+          <t>1,91; 23,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,29; 24,58</t>
+          <t>4,08; 24,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,96; 28,75</t>
+          <t>15,17; 28,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 41,99</t>
+          <t>-28,59; 46,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,47; 195,93</t>
+          <t>3,22; 203,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,96; 174,52</t>
+          <t>15,26; 181,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>81,83; 275,94</t>
+          <t>86,74; 281,81</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,83; 13,43</t>
+          <t>2,47; 13,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,38; 17,13</t>
+          <t>6,5; 17,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,65; 19,52</t>
+          <t>9,97; 19,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 17,39</t>
+          <t>-8,3; 17,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,68; 57,16</t>
+          <t>8,53; 58,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,33; 71,09</t>
+          <t>22,11; 73,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,09; 104,95</t>
+          <t>43,21; 105,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 71,28</t>
+          <t>-31,63; 70,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/LAWTONB_2R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 22,53</t>
+          <t>-18,26; 22,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,76; 51,02</t>
+          <t>11,29; 49,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 46,29</t>
+          <t>10,03; 48,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 19,29</t>
+          <t>-10,07; 17,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,53; 159,42</t>
+          <t>-56,06; 156,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,08; 278,91</t>
+          <t>25,26; 268,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,31; 346,49</t>
+          <t>26,42; 347,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 50,21</t>
+          <t>-17,99; 44,28</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,33</t>
+          <t>25,33</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>119,96%</t>
+          <t>127,36%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 11,54</t>
+          <t>-15,19; 11,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 27,77</t>
+          <t>-2,19; 28,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,52; 29,81</t>
+          <t>5,65; 31,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,32; 34,18</t>
+          <t>14,92; 35,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,02; 70,21</t>
+          <t>-47,63; 78,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 135,9</t>
+          <t>-7,6; 138,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,16; 291,58</t>
+          <t>25,0; 317,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>44,79; 254,72</t>
+          <t>53,7; 277,41</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 37,3</t>
+          <t>5,52; 36,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 23,76</t>
+          <t>-9,91; 21,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 12,59</t>
+          <t>-15,64; 12,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 26,63</t>
+          <t>4,83; 28,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,76; 311,03</t>
+          <t>15,83; 291,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 133,51</t>
+          <t>-28,15; 125,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,89; 78,19</t>
+          <t>-54,99; 74,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 95,05</t>
+          <t>10,8; 96,54</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,65</t>
+          <t>12,32</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>54,64%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 31,54</t>
+          <t>-1,0; 31,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 28,94</t>
+          <t>-3,71; 30,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 23,66</t>
+          <t>-5,83; 24,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 21,82</t>
+          <t>0,83; 21,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 172,79</t>
+          <t>-3,88; 163,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 118,82</t>
+          <t>-10,58; 125,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 145,53</t>
+          <t>-19,4; 156,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,44; 126,2</t>
+          <t>3,26; 133,08</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>4,12</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 29,92</t>
+          <t>-12,78; 30,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 42,64</t>
+          <t>-0,68; 43,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,79; 52,68</t>
+          <t>18,68; 53,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 15,9</t>
+          <t>-8,76; 15,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,66; 187,63</t>
+          <t>-34,74; 167,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 289,72</t>
+          <t>-2,41; 324,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,59; 937,37</t>
+          <t>92,28; 954,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 92,56</t>
+          <t>-26,64; 88,7</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,58</t>
+          <t>10,87</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 18,16</t>
+          <t>-15,41; 21,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 11,48</t>
+          <t>-22,09; 12,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 20,88</t>
+          <t>-13,26; 21,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 22,15</t>
+          <t>-1,44; 20,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 65,63</t>
+          <t>-34,13; 82,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,33; 44,07</t>
+          <t>-49,9; 51,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,15; 89,91</t>
+          <t>-35,96; 99,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 66,5</t>
+          <t>-3,22; 63,05</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>20,84</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-15,82%</t>
+          <t>112,65%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 25,68</t>
+          <t>3,76; 25,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 21,32</t>
+          <t>-4,71; 19,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,4; 29,15</t>
+          <t>5,68; 29,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 23,31</t>
+          <t>12,16; 29,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,09; 189,01</t>
+          <t>13,28; 185,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 112,28</t>
+          <t>-14,77; 100,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,21; 156,67</t>
+          <t>20,86; 167,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-84,79; 136,14</t>
+          <t>50,48; 212,09</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22,12</t>
+          <t>22,25</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>164,46%</t>
+          <t>160,55%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 12,18</t>
+          <t>-11,45; 11,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,91; 23,5</t>
+          <t>2,72; 24,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 24,26</t>
+          <t>3,72; 24,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,17; 28,1</t>
+          <t>15,27; 28,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,59; 46,74</t>
+          <t>-30,67; 50,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,22; 203,56</t>
+          <t>6,23; 216,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,26; 181,26</t>
+          <t>15,59; 182,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>86,74; 281,81</t>
+          <t>87,47; 281,41</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,83</t>
+          <t>16,57</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>67,08%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 13,45</t>
+          <t>2,38; 13,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,5; 17,41</t>
+          <t>6,4; 17,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,97; 19,34</t>
+          <t>9,57; 19,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 17,37</t>
+          <t>12,99; 20,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,53; 58,15</t>
+          <t>5,96; 54,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,11; 73,81</t>
+          <t>21,23; 74,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,21; 105,0</t>
+          <t>39,71; 102,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 70,31</t>
+          <t>46,45; 89,3</t>
         </is>
       </c>
     </row>
